--- a/reports/latest/Execution_Summary.xlsx
+++ b/reports/latest/Execution_Summary.xlsx
@@ -34,7 +34,7 @@
     <t>Pass Rate (%)</t>
   </si>
   <si>
-    <t>99.22%</t>
+    <t>100.00%</t>
   </si>
   <si>
     <t>Target Pass Threshold (%)</t>
@@ -470,7 +470,7 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>506</v>
+        <v>510</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -478,7 +478,7 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
